--- a/lista_git.xlsx
+++ b/lista_git.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rdcombr-my.sharepoint.com/personal/evtgregoldo_rd_com_br/Documents/backup/18-01-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{0D112544-718F-43F2-AC47-3CE7B27F2A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F675ECD-F5BB-4F5A-BDE3-A450602553DE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{0D112544-718F-43F2-AC47-3CE7B27F2A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C9B5D2A-5F44-480A-A61A-6B5ACA9A51AB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{53F22D57-71FF-46F7-9E60-8F6B59E32035}"/>
   </bookViews>
@@ -88,7 +88,26 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color rgb="FF1F2328"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -99,6 +118,16 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B232C379-33F1-4591-98D0-61A544B2CDE9}" name="lista_git" displayName="lista_git" ref="A1:A2" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:A2" xr:uid="{B232C379-33F1-4591-98D0-61A544B2CDE9}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{44C0EA7D-51B5-4A85-ACB6-DF8F26C0C173}" name="gits_publicos"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,5 +446,8 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>